--- a/course/assets/student-schedule.xlsx
+++ b/course/assets/student-schedule.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>Machine learning 1: what learning means, and regression</t>
+          <t>Machine learning 1: what learning means, and regression (begun)</t>
         </is>
       </c>
       <c r="C13" s="40">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B14" s="71" t="inlineStr">
         <is>
-          <t>Machine learning 2: classification, and judging the prediction</t>
+          <t>Machine learning 2: regression and BigQuery ML (D11 continued), then classification begins</t>
         </is>
       </c>
       <c r="C14" s="71">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B16" s="40" t="inlineStr">
         <is>
-          <t>Machine learning 3: unsupervised learning and clustering</t>
+          <t>Machine learning 3: regression review, classification (D12 continued), then clustering begins</t>
         </is>
       </c>
       <c r="C16" s="40">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B17" s="71" t="inlineStr">
         <is>
-          <t>Machine learning 4: improving models</t>
+          <t>Machine learning 4: clustering (D13 continued), then improving models begins</t>
         </is>
       </c>
       <c r="C17" s="71">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>Machine learning 5: forecasting, explaining and serving predictions</t>
+          <t>Machine learning 5: forests, boosting and better features (D14 continued) · forecasting is optional self-study</t>
         </is>
       </c>
       <c r="C18" s="40">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B19" s="71" t="inlineStr">
         <is>
-          <t>ML capstone on new data, then Power BI Desktop and Power Query I</t>
+          <t>Machine learning 6: explaining and serving predictions, and MLOps; then Power BI Desktop and Power Query I</t>
         </is>
       </c>
       <c r="C19" s="71">

--- a/course/assets/student-schedule.xlsx
+++ b/course/assets/student-schedule.xlsx
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B19" s="71" t="inlineStr">
         <is>
-          <t>Machine learning 6: explaining and serving predictions, and MLOps; then Power BI Desktop and Power Query I</t>
+          <t>Machine learning 6: explaining, MLOps and four models in a row; then Power BI, Fabric and a first report</t>
         </is>
       </c>
       <c r="C19" s="71">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>Power Query II: BigQuery, folding and reusable queries</t>
+          <t>Power Query II: files, append and merge</t>
         </is>
       </c>
       <c r="C20" s="40">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="22" ht="34" customHeight="1" s="35">
       <c r="A22" s="60" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B22" s="40" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Assignment 2, before 4:00 PM Thu 5 Nov (the day after; no class)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" s="35">
       <c r="A23" s="84" t="n">
-        <v>46330</v>
+        <v>46334</v>
       </c>
       <c r="B23" s="71" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E23" s="71" t="inlineStr">
         <is>
-          <t>Assignment 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="71" t="inlineStr">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="24" ht="34" customHeight="1" s="35">
       <c r="A24" s="62" t="n">
-        <v>46331</v>
+        <v>46335</v>
       </c>
       <c r="B24" s="40" t="inlineStr">
         <is>
@@ -1560,13 +1560,13 @@
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Assignment 2, before 4:00 PM</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" s="35">
       <c r="A25" s="85" t="n">
-        <v>46334</v>
+        <v>46337</v>
       </c>
       <c r="B25" s="71" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E25" s="71" t="inlineStr">
         <is>
-          <t>Assignment 4 (due before 4:00 PM Sun 15 Nov)</t>
+          <t>Assignment 3</t>
         </is>
       </c>
       <c r="F25" s="71" t="inlineStr">
@@ -1595,7 +1595,7 @@
     </row>
     <row r="26" ht="34" customHeight="1" s="35">
       <c r="A26" s="64" t="n">
-        <v>46335</v>
+        <v>46341</v>
       </c>
       <c r="B26" s="40" t="inlineStr">
         <is>
@@ -1624,20 +1624,20 @@
     </row>
     <row r="27" ht="34" customHeight="1" s="35">
       <c r="A27" s="86" t="n">
-        <v>46336</v>
+        <v>46342</v>
       </c>
       <c r="B27" s="71" t="inlineStr">
         <is>
-          <t>Generative AI for analysts</t>
+          <t>PL-300 review and weak-area clinic</t>
         </is>
       </c>
       <c r="C27" s="71">
-        <f>HYPERLINK("https://github.com/tatwan/ASAC_Data_Science/blob/main/modules/03-machine-learning-and-ai/README.md","Machine learning and AI literacy")</f>
+        <f>HYPERLINK("https://github.com/tatwan/ASAC_Data_Science/blob/main/modules/08-pl300-and-career-readiness/README.md","PL-300 and career readiness")</f>
         <v/>
       </c>
       <c r="D27" s="72" t="inlineStr">
         <is>
-          <t>After class</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E27" s="71" t="inlineStr">
@@ -1653,11 +1653,11 @@
     </row>
     <row r="28" ht="34" customHeight="1" s="35">
       <c r="A28" s="66" t="n">
-        <v>46337</v>
+        <v>46344</v>
       </c>
       <c r="B28" s="40" t="inlineStr">
         <is>
-          <t>PL-300 review and weak-area clinic</t>
+          <t>Third-party mock and placement handoff</t>
         </is>
       </c>
       <c r="C28" s="40">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D28" s="69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
@@ -1682,20 +1682,20 @@
     </row>
     <row r="29" ht="34" customHeight="1" s="35">
       <c r="A29" s="87" t="n">
-        <v>46338</v>
+        <v>46352</v>
       </c>
       <c r="B29" s="71" t="inlineStr">
         <is>
-          <t>Third-party mock and placement handoff</t>
+          <t>Generative AI for analysts</t>
         </is>
       </c>
       <c r="C29" s="71">
-        <f>HYPERLINK("https://github.com/tatwan/ASAC_Data_Science/blob/main/modules/08-pl300-and-career-readiness/README.md","PL-300 and career readiness")</f>
+        <f>HYPERLINK("https://github.com/tatwan/ASAC_Data_Science/blob/main/modules/03-machine-learning-and-ai/README.md","Machine learning and AI literacy")</f>
         <v/>
       </c>
       <c r="D29" s="72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>After class</t>
         </is>
       </c>
       <c r="E29" s="71" t="inlineStr">
